--- a/DATA/DATA FILES/GAS PACKS DATA.xlsx
+++ b/DATA/DATA FILES/GAS PACKS DATA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex.schwindt\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hoffmanandhoffman-my.sharepoint.com/personal/alex_schwindt_hoffman-hoffman_com/Documents/Desktop/Quick Select App Version 3/DATA/DATA FILES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD341DD-89F0-4EFC-955D-A302FBB6E9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{2FD341DD-89F0-4EFC-955D-A302FBB6E9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DAD0148-2A00-4060-B5D4-F91DC7E89F32}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SCHEDULE" sheetId="1" r:id="rId1"/>
@@ -790,7 +790,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -799,29 +799,29 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1161,7 +1161,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="6.85546875" style="1" customWidth="1"/>
     <col min="5" max="5" width="10.28515625" style="1" customWidth="1"/>
@@ -1206,7 +1206,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:51" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="22" t="s">
         <v>7</v>
       </c>
       <c r="B1" s="23"/>
@@ -1233,7 +1233,7 @@
       <c r="W1" s="23"/>
       <c r="X1" s="23"/>
       <c r="Y1" s="24"/>
-      <c r="AA1" s="29" t="s">
+      <c r="AA1" s="28" t="s">
         <v>8</v>
       </c>
       <c r="AB1" s="23"/>
@@ -1242,7 +1242,7 @@
       <c r="AE1" s="23"/>
       <c r="AF1" s="24"/>
       <c r="AG1" s="16"/>
-      <c r="AH1" s="28" t="s">
+      <c r="AH1" s="22" t="s">
         <v>9</v>
       </c>
       <c r="AI1" s="23"/>
@@ -1264,7 +1264,7 @@
       <c r="AY1" s="24"/>
     </row>
     <row r="2" spans="1:51" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="35" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="23"/>
@@ -1291,22 +1291,22 @@
       <c r="W2" s="23"/>
       <c r="X2" s="23"/>
       <c r="Y2" s="24"/>
-      <c r="AA2" s="29" t="s">
+      <c r="AA2" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="AB2" s="29" t="s">
+      <c r="AB2" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="AC2" s="29" t="s">
+      <c r="AC2" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="AD2" s="29" t="s">
+      <c r="AD2" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="AE2" s="29" t="s">
+      <c r="AE2" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="AF2" s="29" t="s">
+      <c r="AF2" s="28" t="s">
         <v>16</v>
       </c>
       <c r="AG2" s="16"/>
@@ -1366,49 +1366,49 @@
       </c>
     </row>
     <row r="3" spans="1:51" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="32"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="31" t="s">
+      <c r="E3" s="30"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="32"/>
-      <c r="I3" s="32"/>
-      <c r="J3" s="32"/>
-      <c r="K3" s="32"/>
-      <c r="L3" s="32"/>
-      <c r="M3" s="33"/>
-      <c r="N3" s="31" t="s">
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="30"/>
+      <c r="M3" s="31"/>
+      <c r="N3" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="O3" s="32"/>
-      <c r="P3" s="32"/>
-      <c r="Q3" s="32"/>
-      <c r="R3" s="33"/>
-      <c r="S3" s="36" t="s">
+      <c r="O3" s="30"/>
+      <c r="P3" s="30"/>
+      <c r="Q3" s="30"/>
+      <c r="R3" s="31"/>
+      <c r="S3" s="34" t="s">
         <v>41</v>
       </c>
-      <c r="T3" s="34" t="s">
+      <c r="T3" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="U3" s="31" t="s">
+      <c r="U3" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="V3" s="32"/>
-      <c r="W3" s="32"/>
-      <c r="X3" s="33"/>
-      <c r="Y3" s="34" t="s">
+      <c r="V3" s="30"/>
+      <c r="W3" s="30"/>
+      <c r="X3" s="31"/>
+      <c r="Y3" s="27" t="s">
         <v>43</v>
       </c>
       <c r="AA3" s="26"/>
@@ -1501,12 +1501,12 @@
         <v>62</v>
       </c>
       <c r="Y4" s="26"/>
-      <c r="AA4" s="30"/>
-      <c r="AB4" s="30"/>
-      <c r="AC4" s="30"/>
-      <c r="AD4" s="30"/>
-      <c r="AE4" s="30"/>
-      <c r="AF4" s="30"/>
+      <c r="AA4" s="33"/>
+      <c r="AB4" s="33"/>
+      <c r="AC4" s="33"/>
+      <c r="AD4" s="33"/>
+      <c r="AE4" s="33"/>
+      <c r="AF4" s="33"/>
       <c r="AG4" s="16"/>
       <c r="AH4" s="26"/>
       <c r="AI4" s="26"/>
@@ -7525,6 +7525,28 @@
     <row r="126" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="AY2:AY4"/>
+    <mergeCell ref="AN2:AN4"/>
+    <mergeCell ref="N3:R3"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="AA2:AA4"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="AC2:AC4"/>
+    <mergeCell ref="AW2:AW4"/>
+    <mergeCell ref="AX2:AX4"/>
+    <mergeCell ref="A2:Y2"/>
+    <mergeCell ref="AS2:AS4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="AT2:AT4"/>
+    <mergeCell ref="AK2:AK4"/>
+    <mergeCell ref="AM2:AM4"/>
+    <mergeCell ref="AO2:AO4"/>
+    <mergeCell ref="AU2:AU4"/>
+    <mergeCell ref="AP2:AP4"/>
+    <mergeCell ref="AF2:AF4"/>
+    <mergeCell ref="AR2:AR4"/>
+    <mergeCell ref="AH2:AH4"/>
+    <mergeCell ref="AI2:AI4"/>
     <mergeCell ref="A1:Y1"/>
     <mergeCell ref="AJ2:AJ4"/>
     <mergeCell ref="T3:T4"/>
@@ -7541,28 +7563,6 @@
     <mergeCell ref="AB2:AB4"/>
     <mergeCell ref="AD2:AD4"/>
     <mergeCell ref="AH1:AY1"/>
-    <mergeCell ref="AP2:AP4"/>
-    <mergeCell ref="AF2:AF4"/>
-    <mergeCell ref="AR2:AR4"/>
-    <mergeCell ref="AH2:AH4"/>
-    <mergeCell ref="AI2:AI4"/>
-    <mergeCell ref="AT2:AT4"/>
-    <mergeCell ref="AK2:AK4"/>
-    <mergeCell ref="AM2:AM4"/>
-    <mergeCell ref="AO2:AO4"/>
-    <mergeCell ref="AU2:AU4"/>
-    <mergeCell ref="AW2:AW4"/>
-    <mergeCell ref="AX2:AX4"/>
-    <mergeCell ref="A2:Y2"/>
-    <mergeCell ref="AS2:AS4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="AY2:AY4"/>
-    <mergeCell ref="AN2:AN4"/>
-    <mergeCell ref="N3:R3"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="AA2:AA4"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="AC2:AC4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/DATA/DATA FILES/GAS PACKS DATA.xlsx
+++ b/DATA/DATA FILES/GAS PACKS DATA.xlsx
@@ -1429,6 +1429,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1551,6 +1561,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1673,6 +1693,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1795,6 +1825,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1917,6 +1957,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2039,6 +2089,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2161,6 +2221,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2283,6 +2353,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2405,6 +2485,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2527,6 +2617,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2649,6 +2749,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2771,6 +2881,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2893,6 +3013,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3015,6 +3145,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3137,6 +3277,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3259,6 +3409,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3381,6 +3541,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3503,6 +3673,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3625,6 +3805,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3747,6 +3937,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3869,6 +4069,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3991,6 +4201,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4113,6 +4333,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4235,6 +4465,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4357,6 +4597,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4479,6 +4729,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4601,6 +4861,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4723,6 +4993,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4845,6 +5125,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4967,6 +5257,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5089,6 +5389,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5211,6 +5521,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5333,6 +5653,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5455,6 +5785,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5577,6 +5917,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5699,6 +6049,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5821,6 +6181,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5943,6 +6313,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6065,6 +6445,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6187,6 +6577,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6309,6 +6709,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6431,6 +6841,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6553,6 +6973,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6675,6 +7105,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6797,6 +7237,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6919,6 +7369,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7041,6 +7501,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7163,6 +7633,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7285,6 +7765,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7407,6 +7897,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7529,6 +8029,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7651,6 +8161,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7773,6 +8293,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7895,6 +8425,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -8017,6 +8557,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -8139,6 +8689,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -8261,6 +8821,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -8383,6 +8953,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -8505,6 +9085,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8627,6 +9217,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8749,6 +9349,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8871,6 +9481,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8993,6 +9613,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -9115,6 +9745,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -9237,6 +9877,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -9359,6 +10009,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -9481,6 +10141,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -9603,6 +10273,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -9725,6 +10405,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -9847,6 +10537,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -9969,6 +10669,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -10091,6 +10801,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -10213,6 +10933,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -10335,6 +11065,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -10457,6 +11197,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -10579,6 +11329,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -10701,6 +11461,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -10823,6 +11593,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -10945,6 +11725,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -11067,6 +11857,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -11189,6 +11989,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -11311,6 +12121,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -11433,6 +12253,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -11555,6 +12385,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -11677,6 +12517,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -11799,6 +12649,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -11921,6 +12781,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -12043,6 +12913,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -12165,6 +13045,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -12287,6 +13177,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -12409,6 +13309,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -12531,6 +13441,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -12653,6 +13573,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -12775,6 +13705,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -12897,6 +13837,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -13019,6 +13969,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -13141,6 +14101,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -13263,6 +14233,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -13385,6 +14365,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -13507,6 +14497,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -13629,6 +14629,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -13751,6 +14761,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -13873,6 +14893,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -13995,6 +15025,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -14117,6 +15157,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -14239,6 +15289,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -14361,6 +15421,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -14483,6 +15553,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -14605,6 +15685,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -14727,6 +15817,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -14849,6 +15949,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -14971,6 +16081,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -15093,6 +16213,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -15215,6 +16345,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -15337,6 +16477,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -15459,6 +16609,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -15581,6 +16741,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -15703,6 +16873,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -15825,6 +17005,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -15947,6 +17137,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -16069,6 +17269,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="15.75" customHeight="1" thickBot="1">
       <c r="A126" t="inlineStr">
@@ -16191,6 +17401,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -16313,6 +17533,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -16435,6 +17665,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -16557,6 +17797,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -16679,6 +17929,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -16801,6 +18061,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -16923,6 +18193,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -17045,6 +18325,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -17167,6 +18457,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -17289,6 +18589,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -17411,6 +18721,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -17533,6 +18853,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -17655,6 +18985,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -17777,6 +19117,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -17899,6 +19249,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -18021,6 +19381,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -18143,6 +19513,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -18265,6 +19645,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -18387,6 +19777,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -18509,6 +19909,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -18631,6 +20041,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -18753,6 +20173,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -18875,6 +20305,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -18997,6 +20437,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -19119,6 +20569,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -19241,6 +20701,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -19363,6 +20833,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -19485,6 +20965,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -19607,6 +21097,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -19729,6 +21229,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -19851,6 +21361,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -19973,6 +21493,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -20095,6 +21625,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -20217,6 +21757,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -20339,6 +21889,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -20461,6 +22021,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -20583,6 +22153,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -20705,6 +22285,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -20827,6 +22417,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -20949,6 +22549,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -21071,6 +22681,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -21193,6 +22813,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -21315,6 +22945,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -21437,6 +23077,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -21559,6 +23209,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -21681,6 +23341,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -21803,6 +23473,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -21925,6 +23605,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -22047,6 +23737,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ174" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK174" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -22169,6 +23869,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -22291,6 +24001,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK176" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -22413,6 +24133,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -22535,6 +24265,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ178" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK178" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -22657,6 +24397,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -22779,6 +24529,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -22901,6 +24661,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ181" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK181" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -23023,6 +24793,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -23145,6 +24925,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -23267,6 +25057,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -23389,6 +25189,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -23511,6 +25321,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ186" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK186" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -23633,6 +25453,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -23755,6 +25585,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ188" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK188" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -23877,6 +25717,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ189" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -23999,6 +25849,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ190" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK190" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -24121,6 +25981,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ191" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -24243,6 +26113,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ192" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -24365,6 +26245,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -24487,6 +26377,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ194" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -24609,6 +26509,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ195" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK195" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -24731,6 +26641,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ196" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK196" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -24853,6 +26773,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -24975,6 +26905,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ198" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK198" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -25097,6 +27037,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -25219,6 +27169,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ200" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK200" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -25341,6 +27301,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ201" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -25463,6 +27433,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ202" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -25585,6 +27565,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -25707,6 +27697,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ204" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK204" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -25829,6 +27829,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ205" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -25951,6 +27961,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ206" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -26073,6 +28093,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ207" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -26195,6 +28225,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ208" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK208" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -26317,6 +28357,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ209" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -26439,6 +28489,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -26561,6 +28621,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ211" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -26683,6 +28753,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -26805,6 +28885,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ213" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK213" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -26927,6 +29017,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ214" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK214" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -27049,6 +29149,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ215" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK215" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -27171,6 +29281,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ216" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK216" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -27293,6 +29413,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ217" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK217" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -27415,6 +29545,16 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AJ218" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK218" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -27537,6 +29677,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ219" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK219" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -27659,6 +29809,16 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AJ220" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
+        </is>
+      </c>
+      <c r="AK220" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -27781,6 +29941,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK221" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -27903,6 +30068,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK222" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -28025,6 +30195,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK223" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -28147,6 +30322,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK224" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -28269,6 +30449,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK225" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -28391,6 +30576,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK226" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -28513,6 +30703,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK227" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -28635,6 +30830,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK228" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -28757,6 +30957,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK229" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -28879,6 +31084,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK230" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -29001,6 +31211,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK231" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -29123,6 +31338,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK232" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -29245,6 +31465,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK233" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -29367,6 +31592,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK234" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -29489,6 +31719,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK235" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -29611,6 +31846,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK236" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -29733,6 +31973,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK237" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -29855,6 +32100,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK238" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -29977,6 +32227,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK239" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -30099,6 +32354,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK240" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -30221,6 +32481,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK241" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -30343,6 +32608,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK242" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -30465,6 +32735,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK243" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -30587,6 +32862,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK244" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -30709,6 +32989,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK245" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -30831,6 +33116,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK246" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -30953,6 +33243,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK247" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -31075,6 +33370,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK248" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -31197,6 +33497,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK249" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -31319,6 +33624,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK250" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -31441,6 +33751,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK251" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -31563,6 +33878,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK252" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -31685,6 +34005,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK253" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -31807,6 +34132,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK254" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -31929,6 +34259,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK255" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -32051,6 +34386,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK256" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -32173,6 +34513,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK257" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -32295,6 +34640,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK258" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -32417,6 +34767,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK259" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -32539,6 +34894,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK260" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -32661,6 +35021,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK261" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -32783,6 +35148,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK262" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -32905,6 +35275,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK263" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -33027,6 +35402,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK264" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -33149,6 +35529,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK265" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -33271,6 +35656,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK266" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -33393,6 +35783,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK267" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -33515,6 +35910,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK268" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -33637,6 +36037,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK269" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -33759,6 +36164,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK270" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -33881,6 +36291,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK271" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -34003,6 +36418,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK272" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -34125,6 +36545,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK273" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -34247,6 +36672,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK274" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -34369,6 +36799,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK275" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -34491,6 +36926,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK276" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -34613,6 +37053,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK277" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -34735,6 +37180,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK278" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -34857,6 +37307,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK279" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -34979,6 +37434,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK280" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -35101,6 +37561,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK281" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -35223,6 +37688,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK282" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -35345,6 +37815,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK283" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -35467,6 +37942,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK284" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -35589,6 +38069,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK285" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -35711,6 +38196,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK286" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -35833,6 +38323,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK287" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -35955,6 +38450,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK288" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -36077,6 +38577,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK289" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -36199,6 +38704,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK290" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -36321,6 +38831,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK291" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -36443,6 +38958,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK292" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -36565,6 +39085,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK293" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -36687,6 +39212,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK294" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -36809,6 +39339,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK295" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -36931,6 +39466,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK296" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -37053,6 +39593,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK297" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -37175,6 +39720,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK298" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -37297,6 +39847,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK299" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -37419,6 +39974,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK300" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -37541,6 +40101,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK301" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -37663,6 +40228,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK302" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -37785,6 +40355,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK303" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -37907,6 +40482,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK304" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -38029,6 +40609,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK305" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -38151,6 +40736,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK306" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -38273,6 +40863,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK307" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -38395,6 +40990,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK308" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -38517,6 +41117,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK309" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -38639,6 +41244,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK310" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -38761,6 +41371,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK311" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -38883,6 +41498,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK312" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -39005,6 +41625,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK313" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -39127,6 +41752,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK314" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -39249,6 +41879,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK315" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -39371,6 +42006,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK316" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -39493,6 +42133,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK317" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -39615,6 +42260,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK318" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -39737,6 +42387,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK319" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -39859,6 +42514,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK320" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -39981,6 +42641,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK321" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -40103,6 +42768,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK322" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -40225,6 +42895,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK323" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -40347,6 +43022,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK324" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -40469,6 +43149,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK325" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -40591,6 +43276,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK326" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -40713,6 +43403,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK327" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -40835,6 +43530,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK328" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -40957,6 +43657,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK329" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -41079,6 +43784,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK330" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -41201,6 +43911,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK331" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -41323,6 +44038,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK332" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -41445,6 +44165,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK333" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -41567,6 +44292,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK334" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -41689,6 +44419,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK335" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -41811,6 +44546,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK336" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -41933,6 +44673,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK337" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -42055,6 +44800,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK338" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -42177,6 +44927,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK339" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -42299,6 +45054,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK340" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Choice LV 15-27.5 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -42421,6 +45181,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK341" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -42543,6 +45308,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK342" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -42665,6 +45435,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK343" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -42787,6 +45562,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK344" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -42909,6 +45689,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK345" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -43031,6 +45816,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK346" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -43153,6 +45943,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK347" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -43275,6 +46070,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK348" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -43397,6 +46197,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK349" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -43519,6 +46324,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK350" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -43641,6 +46451,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK351" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -43763,6 +46578,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK352" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -43885,6 +46705,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK353" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -44007,6 +46832,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK354" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -44129,6 +46959,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK355" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -44251,6 +47086,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK356" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -44373,6 +47213,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK357" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -44495,6 +47340,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK358" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -44617,6 +47467,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK359" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -44739,6 +47594,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK360" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -44861,6 +47721,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK361" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -44983,6 +47848,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK362" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -45105,6 +47975,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK363" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -45227,6 +48102,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK364" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -45349,6 +48229,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK365" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -45471,6 +48356,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK366" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -45593,6 +48483,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK367" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -45715,6 +48610,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK368" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -45837,6 +48737,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK369" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -45959,6 +48864,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK370" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -46081,6 +48991,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK371" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -46203,6 +49118,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK372" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -46325,6 +49245,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK373" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -46447,6 +49372,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK374" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -46569,6 +49499,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK375" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -46691,6 +49626,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK376" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -46813,6 +49753,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK377" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -46935,6 +49880,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK378" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -47057,6 +50007,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK379" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -47179,6 +50134,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK380" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -47301,6 +50261,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK381" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -47423,6 +50388,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK382" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -47545,6 +50515,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK383" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -47667,6 +50642,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK384" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -47789,6 +50769,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK385" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -47911,6 +50896,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK386" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -48033,6 +51023,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK387" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -48155,6 +51150,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK388" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -48277,6 +51277,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK389" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -48399,6 +51404,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK390" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -48521,6 +51531,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK391" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -48643,6 +51658,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK392" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -48765,6 +51785,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK393" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -48887,6 +51912,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK394" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -49009,6 +52039,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK395" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -49131,6 +52166,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK396" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -49253,6 +52293,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK397" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -49375,6 +52420,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK398" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -49497,6 +52547,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK399" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -49619,6 +52674,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK400" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -49741,6 +52801,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK401" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -49863,6 +52928,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK402" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -49985,6 +53055,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK403" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -50107,6 +53182,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK404" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -50229,6 +53309,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK405" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -50351,6 +53436,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK406" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -50473,6 +53563,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK407" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -50595,6 +53690,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK408" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -50717,6 +53817,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK409" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -50839,6 +53944,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK410" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -50961,6 +54071,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK411" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -51083,6 +54198,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK412" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -51205,6 +54325,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK413" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -51327,6 +54452,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK414" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -51449,6 +54579,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK415" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -51571,6 +54706,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK416" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -51693,6 +54833,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK417" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -51815,6 +54960,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK418" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -51937,6 +55087,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK419" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -52059,6 +55214,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK420" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -52181,6 +55341,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK421" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -52303,6 +55468,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK422" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -52425,6 +55595,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK423" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -52547,6 +55722,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK424" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -52669,6 +55849,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK425" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -52791,6 +55976,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK426" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -52913,6 +56103,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK427" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -53035,6 +56230,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK428" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -53157,6 +56357,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK429" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -53279,6 +56484,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK430" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -53401,6 +56611,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK431" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -53523,6 +56738,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK432" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -53645,6 +56865,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK433" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -53767,6 +56992,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK434" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -53889,6 +57119,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK435" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -54011,6 +57246,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK436" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -54133,6 +57373,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK437" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -54255,6 +57500,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK438" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -54377,6 +57627,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK439" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -54499,6 +57754,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK440" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -54621,6 +57881,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK441" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -54743,6 +58008,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK442" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -54865,6 +58135,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK443" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -54987,6 +58262,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK444" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -55109,6 +58389,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK445" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -55231,6 +58516,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK446" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -55353,6 +58643,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK447" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
@@ -55475,6 +58770,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK448" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
@@ -55597,6 +58897,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK449" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
@@ -55719,6 +59024,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK450" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
@@ -55841,6 +59151,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK451" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
@@ -55963,6 +59278,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK452" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
@@ -56085,6 +59405,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK453" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
@@ -56207,6 +59532,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK454" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
@@ -56329,6 +59659,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK455" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -56451,6 +59786,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK456" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
@@ -56573,6 +59913,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK457" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
@@ -56695,6 +60040,11 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
+      <c r="AK458" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
@@ -56817,6 +60167,11 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
+      <c r="AK459" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -56937,6 +60292,11 @@
       <c r="AG460" t="inlineStr">
         <is>
           <t>HIGH STATIC</t>
+        </is>
+      </c>
+      <c r="AK460" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Select RV 27.5-50 Ton Technical Guide</t>
         </is>
       </c>
     </row>

--- a/DATA/DATA FILES/GAS PACKS DATA.xlsx
+++ b/DATA/DATA FILES/GAS PACKS DATA.xlsx
@@ -822,7 +822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY460"/>
+  <dimension ref="A1:AZ460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" width="7.42578125" customWidth="1" style="1" min="1" max="1"/>
@@ -866,7 +866,7 @@
     <col width="14.5703125" customWidth="1" style="10" min="48" max="49"/>
     <col width="20" customWidth="1" style="10" min="50" max="50"/>
     <col width="19.85546875" customWidth="1" style="10" min="51" max="51"/>
-    <col width="9.140625" customWidth="1" style="1" min="52" max="54"/>
+    <col width="19.85546875" customWidth="1" style="1" min="52" max="54"/>
     <col width="9.140625" customWidth="1" style="1" min="55" max="16384"/>
   </cols>
   <sheetData>
@@ -932,7 +932,8 @@
       <c r="AV1" s="23" t="n"/>
       <c r="AW1" s="23" t="n"/>
       <c r="AX1" s="23" t="n"/>
-      <c r="AY1" s="24" t="n"/>
+      <c r="AY1" s="23" t="n"/>
+      <c r="AZ1" s="24" t="n"/>
     </row>
     <row r="2" ht="19.5" customHeight="1" thickBot="1">
       <c r="A2" s="35" t="inlineStr">
@@ -1089,6 +1090,11 @@
           <t>OPERATION MANUAL</t>
         </is>
       </c>
+      <c r="AZ2" s="25" t="inlineStr">
+        <is>
+          <t>PRODUCT DATA SHEET</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" thickBot="1">
       <c r="A3" s="36" t="inlineStr">
@@ -1180,6 +1186,7 @@
       <c r="AW3" s="26" t="n"/>
       <c r="AX3" s="26" t="n"/>
       <c r="AY3" s="26" t="n"/>
+      <c r="AZ3" s="26" t="n"/>
     </row>
     <row r="4" ht="39.95" customHeight="1" thickBot="1">
       <c r="A4" s="26" t="n"/>
@@ -1307,6 +1314,7 @@
       <c r="AW4" s="26" t="n"/>
       <c r="AX4" s="26" t="n"/>
       <c r="AY4" s="26" t="n"/>
+      <c r="AZ4" s="26" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1429,14 +1437,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -1561,14 +1569,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -1693,14 +1701,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -1825,14 +1833,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -1957,14 +1965,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -2089,14 +2097,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -2221,14 +2229,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -2353,14 +2361,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -2485,14 +2493,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ13" t="inlineStr">
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -2617,14 +2625,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ14" t="inlineStr">
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -2749,14 +2757,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ15" t="inlineStr">
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -2881,14 +2889,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ16" t="inlineStr">
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -3013,14 +3021,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ17" t="inlineStr">
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -3145,14 +3153,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ18" t="inlineStr">
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -3277,14 +3285,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ19" t="inlineStr">
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -3409,14 +3417,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ20" t="inlineStr">
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -3541,14 +3549,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ21" t="inlineStr">
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -3673,14 +3681,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ22" t="inlineStr">
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -3805,14 +3813,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ23" t="inlineStr">
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -3937,14 +3945,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ24" t="inlineStr">
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -4069,14 +4077,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ25" t="inlineStr">
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -4201,14 +4209,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ26" t="inlineStr">
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -4333,14 +4341,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ27" t="inlineStr">
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -4465,14 +4473,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ28" t="inlineStr">
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -4597,14 +4605,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ29" t="inlineStr">
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -4729,14 +4737,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ30" t="inlineStr">
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ30" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -4861,14 +4869,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ31" t="inlineStr">
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ31" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -4993,14 +5001,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ32" t="inlineStr">
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ32" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -5125,14 +5133,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ33" t="inlineStr">
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -5257,14 +5265,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ34" t="inlineStr">
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -5389,14 +5397,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ35" t="inlineStr">
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -5521,14 +5529,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ36" t="inlineStr">
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -5653,14 +5661,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ37" t="inlineStr">
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -5785,14 +5793,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ38" t="inlineStr">
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -5917,14 +5925,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ39" t="inlineStr">
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -6049,14 +6057,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ40" t="inlineStr">
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -6181,14 +6189,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ41" t="inlineStr">
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -6313,14 +6321,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ42" t="inlineStr">
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -6445,14 +6453,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ43" t="inlineStr">
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -6577,14 +6585,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ44" t="inlineStr">
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ44" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -6709,14 +6717,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ45" t="inlineStr">
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ45" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -6841,14 +6849,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ46" t="inlineStr">
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -6973,14 +6981,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ47" t="inlineStr">
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -7105,14 +7113,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ48" t="inlineStr">
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ48" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -7237,14 +7245,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ49" t="inlineStr">
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ49" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -7369,14 +7377,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ50" t="inlineStr">
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ50" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -7501,14 +7509,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ51" t="inlineStr">
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -7633,14 +7641,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ52" t="inlineStr">
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -7765,14 +7773,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ53" t="inlineStr">
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -7897,14 +7905,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ54" t="inlineStr">
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -8029,14 +8037,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ55" t="inlineStr">
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -8161,14 +8169,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ56" t="inlineStr">
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -8293,14 +8301,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ57" t="inlineStr">
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -8425,14 +8433,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ58" t="inlineStr">
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ58" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -8557,14 +8565,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ59" t="inlineStr">
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -8689,14 +8697,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ60" t="inlineStr">
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ60" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -8821,14 +8829,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ61" t="inlineStr">
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -8953,14 +8961,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ62" t="inlineStr">
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -9085,14 +9093,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ63" t="inlineStr">
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -9217,14 +9225,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ64" t="inlineStr">
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -9349,14 +9357,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ65" t="inlineStr">
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -9481,14 +9489,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ66" t="inlineStr">
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -9613,14 +9621,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ67" t="inlineStr">
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -9745,14 +9753,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ68" t="inlineStr">
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -9877,14 +9885,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ69" t="inlineStr">
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ69" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -10009,14 +10017,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ70" t="inlineStr">
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ70" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -10141,14 +10149,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ71" t="inlineStr">
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ71" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -10273,14 +10281,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ72" t="inlineStr">
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ72" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -10405,14 +10413,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ73" t="inlineStr">
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -10537,14 +10545,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ74" t="inlineStr">
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ74" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -10669,14 +10677,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ75" t="inlineStr">
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ75" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -10801,14 +10809,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ76" t="inlineStr">
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -10933,14 +10941,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ77" t="inlineStr">
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ77" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -11065,14 +11073,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ78" t="inlineStr">
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -11197,14 +11205,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ79" t="inlineStr">
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -11329,14 +11337,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ80" t="inlineStr">
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ80" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -11461,14 +11469,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ81" t="inlineStr">
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ81" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -11593,14 +11601,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ82" t="inlineStr">
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -11725,14 +11733,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ83" t="inlineStr">
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ83" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -11857,14 +11865,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ84" t="inlineStr">
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ84" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -11989,14 +11997,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ85" t="inlineStr">
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ85" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -12121,14 +12129,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ86" t="inlineStr">
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ86" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -12253,14 +12261,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ87" t="inlineStr">
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -12385,14 +12393,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ88" t="inlineStr">
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ88" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -12517,14 +12525,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ89" t="inlineStr">
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -12649,14 +12657,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ90" t="inlineStr">
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -12781,14 +12789,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ91" t="inlineStr">
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -12913,14 +12921,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ92" t="inlineStr">
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -13045,14 +13053,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ93" t="inlineStr">
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -13177,14 +13185,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ94" t="inlineStr">
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -13309,14 +13317,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ95" t="inlineStr">
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -13441,14 +13449,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ96" t="inlineStr">
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -13573,14 +13581,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ97" t="inlineStr">
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -13705,14 +13713,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ98" t="inlineStr">
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -13837,14 +13845,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ99" t="inlineStr">
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -13969,14 +13977,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ100" t="inlineStr">
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -14101,14 +14109,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ101" t="inlineStr">
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -14233,14 +14241,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ102" t="inlineStr">
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -14365,14 +14373,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ103" t="inlineStr">
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -14497,14 +14505,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ104" t="inlineStr">
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -14629,14 +14637,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ105" t="inlineStr">
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -14761,14 +14769,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ106" t="inlineStr">
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -14893,14 +14901,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ107" t="inlineStr">
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ107" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -15025,14 +15033,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ108" t="inlineStr">
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ108" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -15157,14 +15165,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ109" t="inlineStr">
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ109" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -15289,14 +15297,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ110" t="inlineStr">
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ110" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -15421,14 +15429,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ111" t="inlineStr">
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ111" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -15553,14 +15561,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ112" t="inlineStr">
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ112" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -15685,14 +15693,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ113" t="inlineStr">
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ113" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -15817,14 +15825,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ114" t="inlineStr">
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ114" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -15949,14 +15957,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ115" t="inlineStr">
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ115" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -16081,14 +16089,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ116" t="inlineStr">
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ116" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -16213,14 +16221,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ117" t="inlineStr">
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ117" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -16345,14 +16353,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ118" t="inlineStr">
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ118" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -16477,14 +16485,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ119" t="inlineStr">
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -16609,14 +16617,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ120" t="inlineStr">
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ120" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -16741,14 +16749,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ121" t="inlineStr">
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -16873,14 +16881,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ122" t="inlineStr">
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -17005,14 +17013,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ123" t="inlineStr">
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -17137,14 +17145,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ124" t="inlineStr">
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -17269,14 +17277,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ125" t="inlineStr">
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -17401,14 +17409,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ126" t="inlineStr">
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK126" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -17533,14 +17541,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ127" t="inlineStr">
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK127" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -17665,14 +17673,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ128" t="inlineStr">
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -17797,14 +17805,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ129" t="inlineStr">
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK129" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -17929,14 +17937,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ130" t="inlineStr">
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -18061,14 +18069,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ131" t="inlineStr">
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ131" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -18193,14 +18201,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ132" t="inlineStr">
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ132" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK132" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -18325,14 +18333,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ133" t="inlineStr">
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ133" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK133" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -18457,14 +18465,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ134" t="inlineStr">
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ134" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -18589,14 +18597,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ135" t="inlineStr">
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ135" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -18721,14 +18729,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ136" t="inlineStr">
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ136" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -18853,14 +18861,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ137" t="inlineStr">
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ137" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK137" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -18985,14 +18993,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ138" t="inlineStr">
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ138" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK138" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -19117,14 +19125,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ139" t="inlineStr">
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ139" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK139" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -19249,14 +19257,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ140" t="inlineStr">
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ140" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK140" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -19381,14 +19389,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ141" t="inlineStr">
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ141" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK141" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -19513,14 +19521,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ142" t="inlineStr">
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ142" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK142" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -19645,14 +19653,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ143" t="inlineStr">
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK143" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -19777,14 +19785,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ144" t="inlineStr">
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ144" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -19909,14 +19917,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ145" t="inlineStr">
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ145" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -20041,14 +20049,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ146" t="inlineStr">
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ146" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK146" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -20173,14 +20181,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ147" t="inlineStr">
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ147" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK147" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -20305,14 +20313,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ148" t="inlineStr">
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ148" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK148" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -20437,14 +20445,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ149" t="inlineStr">
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ149" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK149" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -20569,14 +20577,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ150" t="inlineStr">
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ150" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK150" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -20701,14 +20709,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ151" t="inlineStr">
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ151" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK151" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -20833,14 +20841,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ152" t="inlineStr">
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ152" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -20965,14 +20973,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ153" t="inlineStr">
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ153" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK153" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -21097,14 +21105,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ154" t="inlineStr">
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ154" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK154" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -21229,14 +21237,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ155" t="inlineStr">
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ155" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK155" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -21361,14 +21369,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ156" t="inlineStr">
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ156" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK156" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -21493,14 +21501,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ157" t="inlineStr">
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ157" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK157" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -21625,14 +21633,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ158" t="inlineStr">
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ158" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK158" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -21757,14 +21765,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ159" t="inlineStr">
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ159" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK159" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -21889,14 +21897,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ160" t="inlineStr">
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ160" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK160" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -22021,14 +22029,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ161" t="inlineStr">
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ161" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK161" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -22153,14 +22161,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ162" t="inlineStr">
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ162" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK162" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -22285,14 +22293,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ163" t="inlineStr">
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK163" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -22417,14 +22425,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ164" t="inlineStr">
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK164" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -22549,14 +22557,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ165" t="inlineStr">
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ165" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -22681,14 +22689,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ166" t="inlineStr">
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK166" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -22813,14 +22821,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ167" t="inlineStr">
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK167" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -22945,14 +22953,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ168" t="inlineStr">
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ168" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK168" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -23077,14 +23085,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ169" t="inlineStr">
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ169" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK169" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -23209,14 +23217,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ170" t="inlineStr">
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ170" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK170" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -23341,14 +23349,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ171" t="inlineStr">
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ171" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK171" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -23473,14 +23481,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ172" t="inlineStr">
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ172" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK172" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -23605,14 +23613,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ173" t="inlineStr">
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ173" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK173" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -23737,14 +23745,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ174" t="inlineStr">
+      <c r="AK174" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ174" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK174" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -23869,14 +23877,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ175" t="inlineStr">
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ175" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK175" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -24001,14 +24009,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ176" t="inlineStr">
+      <c r="AK176" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ176" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK176" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -24133,14 +24141,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ177" t="inlineStr">
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ177" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK177" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -24265,14 +24273,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ178" t="inlineStr">
+      <c r="AK178" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ178" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK178" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -24397,14 +24405,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ179" t="inlineStr">
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ179" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK179" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -24529,14 +24537,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ180" t="inlineStr">
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ180" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK180" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -24661,14 +24669,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ181" t="inlineStr">
+      <c r="AK181" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ181" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK181" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -24793,14 +24801,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ182" t="inlineStr">
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ182" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK182" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -24925,14 +24933,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ183" t="inlineStr">
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ183" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK183" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -25057,14 +25065,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ184" t="inlineStr">
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ184" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK184" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -25189,14 +25197,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ185" t="inlineStr">
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ185" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK185" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -25321,14 +25329,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ186" t="inlineStr">
+      <c r="AK186" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ186" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK186" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -25453,14 +25461,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ187" t="inlineStr">
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ187" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK187" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -25585,14 +25593,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ188" t="inlineStr">
+      <c r="AK188" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ188" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK188" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -25717,14 +25725,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ189" t="inlineStr">
+      <c r="AK189" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ189" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK189" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -25849,14 +25857,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ190" t="inlineStr">
+      <c r="AK190" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ190" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK190" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -25981,14 +25989,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ191" t="inlineStr">
+      <c r="AK191" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ191" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK191" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -26113,14 +26121,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ192" t="inlineStr">
+      <c r="AK192" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ192" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK192" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -26245,14 +26253,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ193" t="inlineStr">
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ193" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK193" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -26377,14 +26385,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ194" t="inlineStr">
+      <c r="AK194" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ194" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK194" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -26509,14 +26517,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ195" t="inlineStr">
+      <c r="AK195" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ195" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK195" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -26641,14 +26649,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ196" t="inlineStr">
+      <c r="AK196" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ196" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK196" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -26773,14 +26781,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ197" t="inlineStr">
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ197" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK197" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -26905,14 +26913,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ198" t="inlineStr">
+      <c r="AK198" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ198" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK198" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -27037,14 +27045,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ199" t="inlineStr">
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ199" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK199" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -27169,14 +27177,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ200" t="inlineStr">
+      <c r="AK200" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ200" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK200" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -27301,14 +27309,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ201" t="inlineStr">
+      <c r="AK201" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ201" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK201" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -27433,14 +27441,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ202" t="inlineStr">
+      <c r="AK202" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ202" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK202" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -27565,14 +27573,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ203" t="inlineStr">
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ203" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK203" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -27697,14 +27705,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ204" t="inlineStr">
+      <c r="AK204" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ204" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK204" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -27829,14 +27837,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ205" t="inlineStr">
+      <c r="AK205" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ205" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK205" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -27961,14 +27969,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ206" t="inlineStr">
+      <c r="AK206" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ206" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK206" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -28093,14 +28101,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ207" t="inlineStr">
+      <c r="AK207" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ207" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK207" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -28225,14 +28233,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ208" t="inlineStr">
+      <c r="AK208" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ208" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK208" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -28357,14 +28365,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ209" t="inlineStr">
+      <c r="AK209" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ209" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK209" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -28489,14 +28497,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ210" t="inlineStr">
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ210" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK210" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -28621,14 +28629,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ211" t="inlineStr">
+      <c r="AK211" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ211" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK211" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -28753,14 +28761,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ212" t="inlineStr">
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ212" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK212" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -28885,14 +28893,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ213" t="inlineStr">
+      <c r="AK213" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ213" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK213" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -29017,14 +29025,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ214" t="inlineStr">
+      <c r="AK214" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ214" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK214" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -29149,14 +29157,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ215" t="inlineStr">
+      <c r="AK215" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ215" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK215" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -29281,14 +29289,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ216" t="inlineStr">
+      <c r="AK216" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ216" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK216" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -29413,14 +29421,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ217" t="inlineStr">
+      <c r="AK217" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ217" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK217" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -29545,14 +29553,14 @@
           <t>STANDARD STATIC</t>
         </is>
       </c>
-      <c r="AJ218" t="inlineStr">
+      <c r="AK218" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ218" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK218" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -29677,14 +29685,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ219" t="inlineStr">
+      <c r="AK219" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ219" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK219" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -29809,14 +29817,14 @@
           <t>HIGH STATIC</t>
         </is>
       </c>
-      <c r="AJ220" t="inlineStr">
+      <c r="AK220" t="inlineStr">
+        <is>
+          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
+        </is>
+      </c>
+      <c r="AZ220" t="inlineStr">
         <is>
           <t>TempMaster Omni Pro KJ 3-12.5 Ton Submittal Data Sheet</t>
-        </is>
-      </c>
-      <c r="AK220" t="inlineStr">
-        <is>
-          <t>TempMaster Omni Pro KJ 3-12.5 Ton Technical Guide</t>
         </is>
       </c>
     </row>
@@ -60301,17 +60309,17 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="40">
     <mergeCell ref="A2:Y2"/>
     <mergeCell ref="AS2:AS4"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="AY2:AY4"/>
     <mergeCell ref="AN2:AN4"/>
-    <mergeCell ref="AH1:AY1"/>
     <mergeCell ref="AP2:AP4"/>
     <mergeCell ref="AF2:AF4"/>
     <mergeCell ref="AR2:AR4"/>
     <mergeCell ref="AH2:AH4"/>
+    <mergeCell ref="AZ2:AZ4"/>
     <mergeCell ref="N3:R3"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="AT2:AT4"/>
@@ -60331,6 +60339,7 @@
     <mergeCell ref="AL2:AL4"/>
     <mergeCell ref="AV2:AV4"/>
     <mergeCell ref="AX2:AX4"/>
+    <mergeCell ref="AH1:AZ1"/>
     <mergeCell ref="G3:M3"/>
     <mergeCell ref="C3:C4"/>
     <mergeCell ref="AG2:AG4"/>
